--- a/template_51.xlsx
+++ b/template_51.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB494839-4EDE-44DA-A71B-FB071F3171D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7F636A-F143-4896-ABD2-FC2FCDC98BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FAACB0CA-ECFE-4A80-A522-B80854A669FD}"/>
+    <workbookView xWindow="1656" yWindow="456" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{FAACB0CA-ECFE-4A80-A522-B80854A669FD}"/>
   </bookViews>
   <sheets>
     <sheet name="ค่าทำงาน" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="47">
   <si>
     <t>งานเดินรถแขวงธนบุรี  กองจัดการเดินรถเขต 4  ฝ่ายปฏิบัติการเดินรถ</t>
   </si>
@@ -177,13 +177,16 @@
   </si>
   <si>
     <t>วันที่ 16-[N] [PMONTH] 2569</t>
+  </si>
+  <si>
+    <t>0+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,7 +198,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="222"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -490,14 +493,32 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -524,24 +545,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -863,7 +866,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:AS31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="3" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" style="4" customWidth="1"/>
@@ -879,115 +882,115 @@
     <col min="43" max="43" width="1.77734375" style="5" customWidth="1"/>
     <col min="44" max="44" width="2.33203125" style="5" customWidth="1"/>
     <col min="45" max="45" width="2.6640625" style="5" customWidth="1"/>
-    <col min="46" max="16384" width="9" style="43"/>
+    <col min="46" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="42" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:45" s="27" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="33" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
+      <c r="AK1" s="38"/>
+      <c r="AL1" s="38"/>
+      <c r="AM1" s="38"/>
+      <c r="AN1" s="38"/>
+      <c r="AO1" s="38"/>
+      <c r="AP1" s="38"/>
+      <c r="AQ1" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="33"/>
-      <c r="AS1" s="33"/>
-    </row>
-    <row r="2" spans="1:45" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+    </row>
+    <row r="2" spans="1:45" s="27" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38"/>
+      <c r="AM2" s="38"/>
+      <c r="AN2" s="38"/>
+      <c r="AO2" s="38"/>
+      <c r="AP2" s="38"/>
       <c r="AQ2" s="2"/>
       <c r="AR2" s="2"/>
       <c r="AS2" s="2"/>
     </row>
-    <row r="3" spans="1:45" ht="3.75" customHeight="1"/>
-    <row r="4" spans="1:45" ht="19.5" customHeight="1">
-      <c r="A4" s="34" t="s">
+    <row r="3" spans="1:45" ht="3.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:45" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -996,59 +999,59 @@
       <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="37" t="s">
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="34"/>
-      <c r="AI4" s="34"/>
-      <c r="AJ4" s="38" t="s">
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="40"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="30" t="s">
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-    </row>
-    <row r="5" spans="1:45" ht="19.5" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="35"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+    </row>
+    <row r="5" spans="1:45" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="40"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
@@ -1166,16 +1169,16 @@
       <c r="AO5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AP5" s="27" t="s">
+      <c r="AP5" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="40"/>
-      <c r="AR5" s="27" t="s">
+      <c r="AQ5" s="35"/>
+      <c r="AR5" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="AS5" s="27"/>
-    </row>
-    <row r="6" spans="1:45" ht="22.5" customHeight="1">
+      <c r="AS5" s="34"/>
+    </row>
+    <row r="6" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>18</v>
       </c>
@@ -1224,7 +1227,7 @@
       <c r="AR6" s="18"/>
       <c r="AS6" s="20"/>
     </row>
-    <row r="7" spans="1:45" ht="22.5" customHeight="1">
+    <row r="7" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
@@ -1273,7 +1276,7 @@
       <c r="AR7" s="18"/>
       <c r="AS7" s="20"/>
     </row>
-    <row r="8" spans="1:45" ht="22.5" customHeight="1">
+    <row r="8" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>20</v>
       </c>
@@ -1322,7 +1325,7 @@
       <c r="AR8" s="18"/>
       <c r="AS8" s="20"/>
     </row>
-    <row r="9" spans="1:45" ht="22.5" customHeight="1">
+    <row r="9" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
@@ -1371,7 +1374,7 @@
       <c r="AR9" s="18"/>
       <c r="AS9" s="20"/>
     </row>
-    <row r="10" spans="1:45" ht="22.5" customHeight="1">
+    <row r="10" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>22</v>
       </c>
@@ -1420,7 +1423,7 @@
       <c r="AR10" s="18"/>
       <c r="AS10" s="20"/>
     </row>
-    <row r="11" spans="1:45" ht="22.5" customHeight="1">
+    <row r="11" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>23</v>
       </c>
@@ -1469,7 +1472,7 @@
       <c r="AR11" s="18"/>
       <c r="AS11" s="20"/>
     </row>
-    <row r="12" spans="1:45" ht="22.5" customHeight="1">
+    <row r="12" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>24</v>
       </c>
@@ -1518,7 +1521,7 @@
       <c r="AR12" s="18"/>
       <c r="AS12" s="20"/>
     </row>
-    <row r="13" spans="1:45" ht="22.5" customHeight="1">
+    <row r="13" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>25</v>
       </c>
@@ -1567,7 +1570,7 @@
       <c r="AR13" s="18"/>
       <c r="AS13" s="20"/>
     </row>
-    <row r="14" spans="1:45" ht="22.5" customHeight="1">
+    <row r="14" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
@@ -1616,7 +1619,7 @@
       <c r="AR14" s="18"/>
       <c r="AS14" s="20"/>
     </row>
-    <row r="15" spans="1:45" ht="22.5" customHeight="1">
+    <row r="15" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>27</v>
       </c>
@@ -1665,7 +1668,7 @@
       <c r="AR15" s="18"/>
       <c r="AS15" s="20"/>
     </row>
-    <row r="16" spans="1:45" ht="22.5" customHeight="1">
+    <row r="16" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>28</v>
       </c>
@@ -1714,7 +1717,7 @@
       <c r="AR16" s="18"/>
       <c r="AS16" s="20"/>
     </row>
-    <row r="17" spans="1:45" ht="22.5" customHeight="1">
+    <row r="17" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>29</v>
       </c>
@@ -1763,7 +1766,7 @@
       <c r="AR17" s="18"/>
       <c r="AS17" s="20"/>
     </row>
-    <row r="18" spans="1:45" ht="22.5" customHeight="1">
+    <row r="18" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>30</v>
       </c>
@@ -1812,46 +1815,46 @@
       <c r="AR18" s="18"/>
       <c r="AS18" s="20"/>
     </row>
-    <row r="19" spans="1:45" ht="16.5" customHeight="1">
-      <c r="A19" s="28" t="s">
+    <row r="19" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="28"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="29" t="s">
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="AF19" s="29"/>
-      <c r="AG19" s="29"/>
-      <c r="AH19" s="29"/>
-      <c r="AI19" s="29"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="33"/>
+      <c r="AH19" s="33"/>
+      <c r="AI19" s="33"/>
       <c r="AJ19" s="12">
         <f t="shared" ref="AJ19:AO19" si="0">SUM(AJ6:AJ18)</f>
         <v>0</v>
@@ -1876,95 +1879,95 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="30"/>
-      <c r="AQ19" s="31"/>
-      <c r="AR19" s="30"/>
-      <c r="AS19" s="30"/>
-    </row>
-    <row r="20" spans="1:45" ht="0.75" customHeight="1">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
-    </row>
-    <row r="21" spans="1:45" ht="16.5" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="28"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="28"/>
-      <c r="U21" s="28"/>
-      <c r="V21" s="28"/>
-      <c r="W21" s="28"/>
-      <c r="X21" s="28"/>
-      <c r="Y21" s="28"/>
-      <c r="Z21" s="28"/>
-      <c r="AA21" s="28"/>
-      <c r="AB21" s="28"/>
-      <c r="AC21" s="28"/>
-      <c r="AD21" s="28"/>
-      <c r="AE21" s="28"/>
-      <c r="AF21" s="28"/>
-      <c r="AG21" s="28"/>
-      <c r="AH21" s="28"/>
-      <c r="AI21" s="28"/>
-    </row>
-    <row r="22" spans="1:45" ht="16.5" customHeight="1">
+      <c r="AP19" s="36"/>
+      <c r="AQ19" s="37"/>
+      <c r="AR19" s="36"/>
+      <c r="AS19" s="36"/>
+    </row>
+    <row r="20" spans="1:45" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+    </row>
+    <row r="21" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="32"/>
+    </row>
+    <row r="22" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="T22" s="4"/>
     </row>
-    <row r="23" spans="1:45" ht="16.5" customHeight="1">
+    <row r="23" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="22"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:45" s="44" customFormat="1" ht="0.75" customHeight="1">
+    <row r="24" spans="1:45" s="29" customFormat="1" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23"/>
       <c r="B24" s="24"/>
       <c r="C24" s="23"/>
@@ -2011,47 +2014,47 @@
       <c r="AR24" s="25"/>
       <c r="AS24" s="25"/>
     </row>
-    <row r="25" spans="1:45" s="44" customFormat="1" ht="16.5" customHeight="1">
+    <row r="25" spans="1:45" s="29" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23"/>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="I25" s="23"/>
-      <c r="J25" s="39" t="s">
+      <c r="J25" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="39"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
       <c r="T25" s="23"/>
       <c r="U25" s="23"/>
       <c r="V25" s="23"/>
       <c r="W25" s="23"/>
       <c r="X25" s="23"/>
-      <c r="Y25" s="39" t="s">
+      <c r="Y25" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="Z25" s="39"/>
-      <c r="AA25" s="39"/>
-      <c r="AB25" s="39"/>
-      <c r="AC25" s="39"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="39"/>
-      <c r="AF25" s="39"/>
-      <c r="AG25" s="39"/>
-      <c r="AH25" s="39"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="31"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
+      <c r="AH25" s="31"/>
       <c r="AI25" s="23"/>
       <c r="AJ25" s="25"/>
       <c r="AK25" s="25"/>
@@ -2064,7 +2067,7 @@
       <c r="AR25" s="25"/>
       <c r="AS25" s="25"/>
     </row>
-    <row r="26" spans="1:45" s="44" customFormat="1" ht="1.5" customHeight="1">
+    <row r="26" spans="1:45" s="29" customFormat="1" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="23"/>
       <c r="B26" s="24"/>
       <c r="C26" s="23"/>
@@ -2111,7 +2114,7 @@
       <c r="AR26" s="25"/>
       <c r="AS26" s="25"/>
     </row>
-    <row r="27" spans="1:45" s="44" customFormat="1" ht="15.75" customHeight="1">
+    <row r="27" spans="1:45" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23"/>
       <c r="B27" s="24"/>
       <c r="C27" s="23"/>
@@ -2121,9 +2124,9 @@
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
       <c r="M27" s="23"/>
       <c r="N27" s="23"/>
       <c r="O27" s="23"/>
@@ -2136,9 +2139,9 @@
       <c r="V27" s="23"/>
       <c r="W27" s="23"/>
       <c r="X27" s="23"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
       <c r="AB27" s="23"/>
       <c r="AC27" s="23"/>
       <c r="AD27" s="23"/>
@@ -2158,48 +2161,48 @@
       <c r="AR27" s="25"/>
       <c r="AS27" s="25"/>
     </row>
-    <row r="28" spans="1:45" s="44" customFormat="1" ht="15" customHeight="1">
+    <row r="28" spans="1:45" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23"/>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
-      <c r="I28" s="39" t="s">
+      <c r="I28" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="39"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
       <c r="U28" s="23"/>
       <c r="V28" s="23"/>
       <c r="W28" s="23"/>
-      <c r="X28" s="39" t="s">
+      <c r="X28" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="Y28" s="39"/>
-      <c r="Z28" s="39"/>
-      <c r="AA28" s="39"/>
-      <c r="AB28" s="39"/>
-      <c r="AC28" s="39"/>
-      <c r="AD28" s="39"/>
-      <c r="AE28" s="39"/>
-      <c r="AF28" s="39"/>
-      <c r="AG28" s="39"/>
-      <c r="AH28" s="39"/>
-      <c r="AI28" s="39"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
       <c r="AJ28" s="25"/>
       <c r="AK28" s="25"/>
       <c r="AL28" s="25"/>
@@ -2211,47 +2214,47 @@
       <c r="AR28" s="25"/>
       <c r="AS28" s="25"/>
     </row>
-    <row r="29" spans="1:45" s="44" customFormat="1" ht="15" customHeight="1">
+    <row r="29" spans="1:45" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23"/>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
-      <c r="J29" s="39" t="s">
+      <c r="J29" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="39"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
       <c r="T29" s="23"/>
       <c r="U29" s="23"/>
       <c r="V29" s="23"/>
       <c r="W29" s="23"/>
       <c r="X29" s="23"/>
-      <c r="Y29" s="39" t="s">
+      <c r="Y29" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="Z29" s="39"/>
-      <c r="AA29" s="39"/>
-      <c r="AB29" s="39"/>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="39"/>
-      <c r="AE29" s="39"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="39"/>
-      <c r="AH29" s="39"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
+      <c r="AH29" s="31"/>
       <c r="AI29" s="23"/>
       <c r="AJ29" s="25"/>
       <c r="AK29" s="25"/>
@@ -2264,47 +2267,47 @@
       <c r="AR29" s="25"/>
       <c r="AS29" s="25"/>
     </row>
-    <row r="30" spans="1:45" s="44" customFormat="1" ht="15" customHeight="1">
+    <row r="30" spans="1:45" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
-      <c r="J30" s="39" t="s">
+      <c r="J30" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="39"/>
-      <c r="S30" s="39"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
       <c r="T30" s="23"/>
       <c r="U30" s="23"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23"/>
       <c r="X30" s="23"/>
-      <c r="Y30" s="39" t="s">
+      <c r="Y30" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="39"/>
-      <c r="AB30" s="39"/>
-      <c r="AC30" s="39"/>
-      <c r="AD30" s="39"/>
-      <c r="AE30" s="39"/>
-      <c r="AF30" s="39"/>
-      <c r="AG30" s="39"/>
-      <c r="AH30" s="39"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="31"/>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
+      <c r="AH30" s="31"/>
       <c r="AI30" s="23"/>
       <c r="AJ30" s="25"/>
       <c r="AK30" s="25"/>
@@ -2317,86 +2320,61 @@
       <c r="AR30" s="25"/>
       <c r="AS30" s="25"/>
     </row>
-    <row r="31" spans="1:45" s="44" customFormat="1" ht="15" customHeight="1">
+    <row r="31" spans="1:45" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23"/>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="I31" s="23"/>
-      <c r="J31" s="39" t="s">
+      <c r="J31" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="39"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
       <c r="V31" s="23"/>
       <c r="W31" s="23"/>
       <c r="X31" s="23"/>
-      <c r="Y31" s="39" t="s">
+      <c r="Y31" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="Z31" s="39"/>
-      <c r="AA31" s="39"/>
-      <c r="AB31" s="39"/>
-      <c r="AC31" s="39"/>
-      <c r="AD31" s="39"/>
-      <c r="AE31" s="39"/>
-      <c r="AF31" s="39"/>
-      <c r="AG31" s="39"/>
-      <c r="AH31" s="39"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="31"/>
+      <c r="AE31" s="31"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="31"/>
+      <c r="AH31" s="31"/>
       <c r="AI31" s="23"/>
-      <c r="AJ31" s="41"/>
-      <c r="AK31" s="41"/>
-      <c r="AL31" s="41"/>
-      <c r="AM31" s="41"/>
-      <c r="AN31" s="41"/>
-      <c r="AO31" s="41"/>
-      <c r="AP31" s="41"/>
-      <c r="AQ31" s="41"/>
-      <c r="AR31" s="41"/>
-      <c r="AS31" s="41"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="30"/>
+      <c r="AM31" s="30"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="30"/>
+      <c r="AP31" s="30"/>
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="30"/>
+      <c r="AS31" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="AJ31:AS31"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="J30:S30"/>
-    <mergeCell ref="Y30:AH30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="J31:S31"/>
-    <mergeCell ref="Y31:AH31"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="I28:T28"/>
-    <mergeCell ref="X28:AI28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="J29:S29"/>
-    <mergeCell ref="Y29:AH29"/>
-    <mergeCell ref="A21:AI21"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="J25:S25"/>
-    <mergeCell ref="Y25:AH25"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="AP5:AQ5"/>
-    <mergeCell ref="AR5:AS5"/>
-    <mergeCell ref="A19:AD20"/>
-    <mergeCell ref="AE19:AI19"/>
-    <mergeCell ref="AP19:AQ19"/>
-    <mergeCell ref="AR19:AS19"/>
     <mergeCell ref="B1:AP1"/>
     <mergeCell ref="AQ1:AS1"/>
     <mergeCell ref="B2:AP2"/>
@@ -2406,6 +2384,31 @@
     <mergeCell ref="T4:AI4"/>
     <mergeCell ref="AJ4:AK4"/>
     <mergeCell ref="AL4:AS4"/>
+    <mergeCell ref="AP5:AQ5"/>
+    <mergeCell ref="AR5:AS5"/>
+    <mergeCell ref="A19:AD20"/>
+    <mergeCell ref="AE19:AI19"/>
+    <mergeCell ref="AP19:AQ19"/>
+    <mergeCell ref="AR19:AS19"/>
+    <mergeCell ref="A21:AI21"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="J25:S25"/>
+    <mergeCell ref="Y25:AH25"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="I28:T28"/>
+    <mergeCell ref="X28:AI28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="J29:S29"/>
+    <mergeCell ref="Y29:AH29"/>
+    <mergeCell ref="AJ31:AS31"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="J30:S30"/>
+    <mergeCell ref="Y30:AH30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="J31:S31"/>
+    <mergeCell ref="Y31:AH31"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157499" right="0.23622047244094499" top="0.47244094488188998" bottom="0.23622047244094499" header="0.31496062992126" footer="0.31496062992126"/>
@@ -2419,7 +2422,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:AS31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="3" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" style="4" customWidth="1"/>
@@ -2435,115 +2438,115 @@
     <col min="43" max="43" width="1.77734375" style="5" customWidth="1"/>
     <col min="44" max="44" width="2.33203125" style="5" customWidth="1"/>
     <col min="45" max="45" width="2.6640625" style="5" customWidth="1"/>
-    <col min="46" max="16384" width="9" style="43"/>
+    <col min="46" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="42" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:45" s="27" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="33" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
+      <c r="AK1" s="38"/>
+      <c r="AL1" s="38"/>
+      <c r="AM1" s="38"/>
+      <c r="AN1" s="38"/>
+      <c r="AO1" s="38"/>
+      <c r="AP1" s="38"/>
+      <c r="AQ1" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="33"/>
-      <c r="AS1" s="33"/>
-    </row>
-    <row r="2" spans="1:45" s="42" customFormat="1" ht="18" customHeight="1">
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+    </row>
+    <row r="2" spans="1:45" s="27" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38"/>
+      <c r="AM2" s="38"/>
+      <c r="AN2" s="38"/>
+      <c r="AO2" s="38"/>
+      <c r="AP2" s="38"/>
       <c r="AQ2" s="2"/>
       <c r="AR2" s="2"/>
       <c r="AS2" s="2"/>
     </row>
-    <row r="3" spans="1:45" ht="3.75" customHeight="1"/>
-    <row r="4" spans="1:45" ht="19.5" customHeight="1">
-      <c r="A4" s="34" t="s">
+    <row r="3" spans="1:45" ht="3.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:45" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -2552,59 +2555,59 @@
       <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="37" t="s">
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="34"/>
-      <c r="AI4" s="34"/>
-      <c r="AJ4" s="38" t="s">
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="40"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="30" t="s">
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-    </row>
-    <row r="5" spans="1:45" ht="19.5" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="35"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+    </row>
+    <row r="5" spans="1:45" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="40"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
@@ -2722,16 +2725,16 @@
       <c r="AO5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AP5" s="27" t="s">
+      <c r="AP5" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="40"/>
-      <c r="AR5" s="27" t="s">
+      <c r="AQ5" s="35"/>
+      <c r="AR5" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="AS5" s="27"/>
-    </row>
-    <row r="6" spans="1:45" ht="22.5" customHeight="1">
+      <c r="AS5" s="34"/>
+    </row>
+    <row r="6" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>18</v>
       </c>
@@ -2775,12 +2778,16 @@
       <c r="AM6" s="17"/>
       <c r="AN6" s="17"/>
       <c r="AO6" s="17"/>
-      <c r="AP6" s="18"/>
+      <c r="AP6" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ6" s="19"/>
-      <c r="AR6" s="18"/>
+      <c r="AR6" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS6" s="20"/>
     </row>
-    <row r="7" spans="1:45" ht="22.5" customHeight="1">
+    <row r="7" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
@@ -2824,12 +2831,16 @@
       <c r="AM7" s="17"/>
       <c r="AN7" s="17"/>
       <c r="AO7" s="17"/>
-      <c r="AP7" s="18"/>
+      <c r="AP7" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ7" s="19"/>
-      <c r="AR7" s="18"/>
+      <c r="AR7" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS7" s="20"/>
     </row>
-    <row r="8" spans="1:45" ht="22.5" customHeight="1">
+    <row r="8" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>20</v>
       </c>
@@ -2873,12 +2884,16 @@
       <c r="AM8" s="17"/>
       <c r="AN8" s="17"/>
       <c r="AO8" s="17"/>
-      <c r="AP8" s="18"/>
+      <c r="AP8" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ8" s="19"/>
-      <c r="AR8" s="18"/>
+      <c r="AR8" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS8" s="20"/>
     </row>
-    <row r="9" spans="1:45" ht="22.5" customHeight="1">
+    <row r="9" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
@@ -2922,12 +2937,16 @@
       <c r="AM9" s="17"/>
       <c r="AN9" s="17"/>
       <c r="AO9" s="17"/>
-      <c r="AP9" s="18"/>
+      <c r="AP9" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ9" s="19"/>
-      <c r="AR9" s="18"/>
+      <c r="AR9" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS9" s="20"/>
     </row>
-    <row r="10" spans="1:45" ht="22.5" customHeight="1">
+    <row r="10" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>22</v>
       </c>
@@ -2971,12 +2990,16 @@
       <c r="AM10" s="17"/>
       <c r="AN10" s="17"/>
       <c r="AO10" s="17"/>
-      <c r="AP10" s="18"/>
+      <c r="AP10" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ10" s="19"/>
-      <c r="AR10" s="18"/>
+      <c r="AR10" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS10" s="20"/>
     </row>
-    <row r="11" spans="1:45" ht="22.5" customHeight="1">
+    <row r="11" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>23</v>
       </c>
@@ -3020,12 +3043,16 @@
       <c r="AM11" s="17"/>
       <c r="AN11" s="17"/>
       <c r="AO11" s="17"/>
-      <c r="AP11" s="18"/>
+      <c r="AP11" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ11" s="19"/>
-      <c r="AR11" s="18"/>
+      <c r="AR11" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS11" s="20"/>
     </row>
-    <row r="12" spans="1:45" ht="22.5" customHeight="1">
+    <row r="12" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>24</v>
       </c>
@@ -3069,12 +3096,16 @@
       <c r="AM12" s="17"/>
       <c r="AN12" s="17"/>
       <c r="AO12" s="17"/>
-      <c r="AP12" s="18"/>
+      <c r="AP12" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ12" s="19"/>
-      <c r="AR12" s="18"/>
+      <c r="AR12" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS12" s="20"/>
     </row>
-    <row r="13" spans="1:45" ht="22.5" customHeight="1">
+    <row r="13" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>25</v>
       </c>
@@ -3118,12 +3149,16 @@
       <c r="AM13" s="17"/>
       <c r="AN13" s="17"/>
       <c r="AO13" s="17"/>
-      <c r="AP13" s="18"/>
+      <c r="AP13" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ13" s="19"/>
-      <c r="AR13" s="18"/>
+      <c r="AR13" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS13" s="20"/>
     </row>
-    <row r="14" spans="1:45" ht="22.5" customHeight="1">
+    <row r="14" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
@@ -3167,12 +3202,16 @@
       <c r="AM14" s="17"/>
       <c r="AN14" s="17"/>
       <c r="AO14" s="17"/>
-      <c r="AP14" s="18"/>
+      <c r="AP14" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ14" s="19"/>
-      <c r="AR14" s="18"/>
+      <c r="AR14" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS14" s="20"/>
     </row>
-    <row r="15" spans="1:45" ht="22.5" customHeight="1">
+    <row r="15" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>27</v>
       </c>
@@ -3216,12 +3255,16 @@
       <c r="AM15" s="17"/>
       <c r="AN15" s="17"/>
       <c r="AO15" s="17"/>
-      <c r="AP15" s="18"/>
+      <c r="AP15" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ15" s="19"/>
-      <c r="AR15" s="18"/>
+      <c r="AR15" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS15" s="20"/>
     </row>
-    <row r="16" spans="1:45" ht="22.5" customHeight="1">
+    <row r="16" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>28</v>
       </c>
@@ -3265,12 +3308,16 @@
       <c r="AM16" s="17"/>
       <c r="AN16" s="17"/>
       <c r="AO16" s="17"/>
-      <c r="AP16" s="18"/>
+      <c r="AP16" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ16" s="19"/>
-      <c r="AR16" s="18"/>
+      <c r="AR16" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS16" s="20"/>
     </row>
-    <row r="17" spans="1:45" ht="22.5" customHeight="1">
+    <row r="17" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>29</v>
       </c>
@@ -3314,12 +3361,16 @@
       <c r="AM17" s="17"/>
       <c r="AN17" s="17"/>
       <c r="AO17" s="17"/>
-      <c r="AP17" s="18"/>
+      <c r="AP17" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ17" s="19"/>
-      <c r="AR17" s="18"/>
+      <c r="AR17" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS17" s="20"/>
     </row>
-    <row r="18" spans="1:45" ht="22.5" customHeight="1">
+    <row r="18" spans="1:45" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>30</v>
       </c>
@@ -3363,51 +3414,55 @@
       <c r="AM18" s="17"/>
       <c r="AN18" s="17"/>
       <c r="AO18" s="17"/>
-      <c r="AP18" s="18"/>
+      <c r="AP18" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AQ18" s="19"/>
-      <c r="AR18" s="18"/>
+      <c r="AR18" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="AS18" s="20"/>
     </row>
-    <row r="19" spans="1:45" ht="16.5" customHeight="1">
-      <c r="A19" s="28" t="s">
+    <row r="19" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="28"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="29" t="s">
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="AF19" s="29"/>
-      <c r="AG19" s="29"/>
-      <c r="AH19" s="29"/>
-      <c r="AI19" s="29"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="33"/>
+      <c r="AH19" s="33"/>
+      <c r="AI19" s="33"/>
       <c r="AJ19" s="7"/>
       <c r="AK19" s="12">
         <f>SUM(AK6:AK18)</f>
@@ -3417,69 +3472,69 @@
       <c r="AM19" s="7"/>
       <c r="AN19" s="7"/>
       <c r="AO19" s="7"/>
-      <c r="AP19" s="30">
+      <c r="AP19" s="36">
         <f>SUM(AQ6:AQ18)</f>
         <v>0</v>
       </c>
-      <c r="AQ19" s="31"/>
-      <c r="AR19" s="30">
+      <c r="AQ19" s="37"/>
+      <c r="AR19" s="36">
         <f>SUM(AS6:AS18)</f>
         <v>0</v>
       </c>
-      <c r="AS19" s="30"/>
-    </row>
-    <row r="20" spans="1:45" ht="0.75" customHeight="1">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
-    </row>
-    <row r="21" spans="1:45" ht="16.5" customHeight="1">
+      <c r="AS19" s="36"/>
+    </row>
+    <row r="20" spans="1:45" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+    </row>
+    <row r="21" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:45" ht="16.5" customHeight="1">
+    <row r="22" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="T22" s="4"/>
     </row>
-    <row r="23" spans="1:45" ht="16.5" customHeight="1">
+    <row r="23" spans="1:45" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="22"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:45" s="44" customFormat="1" ht="0.75" customHeight="1">
+    <row r="24" spans="1:45" s="29" customFormat="1" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23"/>
       <c r="B24" s="24"/>
       <c r="C24" s="23"/>
@@ -3526,47 +3581,47 @@
       <c r="AR24" s="25"/>
       <c r="AS24" s="25"/>
     </row>
-    <row r="25" spans="1:45" s="44" customFormat="1" ht="16.5" customHeight="1">
+    <row r="25" spans="1:45" s="29" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23"/>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="I25" s="23"/>
-      <c r="J25" s="39" t="s">
+      <c r="J25" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="39"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
       <c r="T25" s="23"/>
       <c r="U25" s="23"/>
       <c r="V25" s="23"/>
       <c r="W25" s="23"/>
       <c r="X25" s="23"/>
-      <c r="Y25" s="39" t="s">
+      <c r="Y25" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="Z25" s="39"/>
-      <c r="AA25" s="39"/>
-      <c r="AB25" s="39"/>
-      <c r="AC25" s="39"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="39"/>
-      <c r="AF25" s="39"/>
-      <c r="AG25" s="39"/>
-      <c r="AH25" s="39"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="31"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
+      <c r="AH25" s="31"/>
       <c r="AI25" s="23"/>
       <c r="AJ25" s="25"/>
       <c r="AK25" s="25"/>
@@ -3579,7 +3634,7 @@
       <c r="AR25" s="25"/>
       <c r="AS25" s="25"/>
     </row>
-    <row r="26" spans="1:45" s="44" customFormat="1" ht="1.5" customHeight="1">
+    <row r="26" spans="1:45" s="29" customFormat="1" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="23"/>
       <c r="B26" s="24"/>
       <c r="C26" s="23"/>
@@ -3626,7 +3681,7 @@
       <c r="AR26" s="25"/>
       <c r="AS26" s="25"/>
     </row>
-    <row r="27" spans="1:45" s="44" customFormat="1" ht="15.75" customHeight="1">
+    <row r="27" spans="1:45" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23"/>
       <c r="B27" s="24"/>
       <c r="C27" s="23"/>
@@ -3636,9 +3691,9 @@
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
       <c r="M27" s="23"/>
       <c r="N27" s="23"/>
       <c r="O27" s="23"/>
@@ -3651,9 +3706,9 @@
       <c r="V27" s="23"/>
       <c r="W27" s="23"/>
       <c r="X27" s="23"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
       <c r="AB27" s="23"/>
       <c r="AC27" s="23"/>
       <c r="AD27" s="23"/>
@@ -3673,48 +3728,48 @@
       <c r="AR27" s="25"/>
       <c r="AS27" s="25"/>
     </row>
-    <row r="28" spans="1:45" s="44" customFormat="1" ht="15" customHeight="1">
+    <row r="28" spans="1:45" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23"/>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
-      <c r="I28" s="39" t="s">
+      <c r="I28" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="39"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
       <c r="U28" s="23"/>
       <c r="V28" s="23"/>
       <c r="W28" s="23"/>
-      <c r="X28" s="39" t="s">
+      <c r="X28" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="Y28" s="39"/>
-      <c r="Z28" s="39"/>
-      <c r="AA28" s="39"/>
-      <c r="AB28" s="39"/>
-      <c r="AC28" s="39"/>
-      <c r="AD28" s="39"/>
-      <c r="AE28" s="39"/>
-      <c r="AF28" s="39"/>
-      <c r="AG28" s="39"/>
-      <c r="AH28" s="39"/>
-      <c r="AI28" s="39"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
       <c r="AJ28" s="25"/>
       <c r="AK28" s="25"/>
       <c r="AL28" s="25"/>
@@ -3726,47 +3781,47 @@
       <c r="AR28" s="25"/>
       <c r="AS28" s="25"/>
     </row>
-    <row r="29" spans="1:45" s="44" customFormat="1" ht="15" customHeight="1">
+    <row r="29" spans="1:45" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23"/>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
-      <c r="J29" s="39" t="s">
+      <c r="J29" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="39"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
       <c r="T29" s="23"/>
       <c r="U29" s="23"/>
       <c r="V29" s="23"/>
       <c r="W29" s="23"/>
       <c r="X29" s="23"/>
-      <c r="Y29" s="39" t="s">
+      <c r="Y29" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="Z29" s="39"/>
-      <c r="AA29" s="39"/>
-      <c r="AB29" s="39"/>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="39"/>
-      <c r="AE29" s="39"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="39"/>
-      <c r="AH29" s="39"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
+      <c r="AH29" s="31"/>
       <c r="AI29" s="23"/>
       <c r="AJ29" s="25"/>
       <c r="AK29" s="25"/>
@@ -3779,47 +3834,47 @@
       <c r="AR29" s="25"/>
       <c r="AS29" s="25"/>
     </row>
-    <row r="30" spans="1:45" s="44" customFormat="1" ht="15" customHeight="1">
+    <row r="30" spans="1:45" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
-      <c r="J30" s="39" t="s">
+      <c r="J30" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="39"/>
-      <c r="S30" s="39"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
       <c r="T30" s="23"/>
       <c r="U30" s="23"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23"/>
       <c r="X30" s="23"/>
-      <c r="Y30" s="39" t="s">
+      <c r="Y30" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="39"/>
-      <c r="AB30" s="39"/>
-      <c r="AC30" s="39"/>
-      <c r="AD30" s="39"/>
-      <c r="AE30" s="39"/>
-      <c r="AF30" s="39"/>
-      <c r="AG30" s="39"/>
-      <c r="AH30" s="39"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="31"/>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
+      <c r="AH30" s="31"/>
       <c r="AI30" s="23"/>
       <c r="AJ30" s="25"/>
       <c r="AK30" s="25"/>
@@ -3832,61 +3887,84 @@
       <c r="AR30" s="25"/>
       <c r="AS30" s="25"/>
     </row>
-    <row r="31" spans="1:45" s="44" customFormat="1" ht="15" customHeight="1">
+    <row r="31" spans="1:45" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23"/>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="I31" s="23"/>
-      <c r="J31" s="39" t="s">
+      <c r="J31" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="39"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
       <c r="V31" s="23"/>
       <c r="W31" s="23"/>
       <c r="X31" s="23"/>
-      <c r="Y31" s="39" t="s">
+      <c r="Y31" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="Z31" s="39"/>
-      <c r="AA31" s="39"/>
-      <c r="AB31" s="39"/>
-      <c r="AC31" s="39"/>
-      <c r="AD31" s="39"/>
-      <c r="AE31" s="39"/>
-      <c r="AF31" s="39"/>
-      <c r="AG31" s="39"/>
-      <c r="AH31" s="39"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="31"/>
+      <c r="AE31" s="31"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="31"/>
+      <c r="AH31" s="31"/>
       <c r="AI31" s="23"/>
-      <c r="AJ31" s="41"/>
-      <c r="AK31" s="41"/>
-      <c r="AL31" s="41"/>
-      <c r="AM31" s="41"/>
-      <c r="AN31" s="41"/>
-      <c r="AO31" s="41"/>
-      <c r="AP31" s="41"/>
-      <c r="AQ31" s="41"/>
-      <c r="AR31" s="41"/>
-      <c r="AS31" s="41"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="30"/>
+      <c r="AM31" s="30"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="30"/>
+      <c r="AP31" s="30"/>
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="30"/>
+      <c r="AS31" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="B1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="B2:AP2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E4:S4"/>
+    <mergeCell ref="T4:AI4"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AS4"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="I28:T28"/>
+    <mergeCell ref="X28:AI28"/>
+    <mergeCell ref="AP5:AQ5"/>
+    <mergeCell ref="AR5:AS5"/>
+    <mergeCell ref="A19:AD20"/>
+    <mergeCell ref="AE19:AI19"/>
+    <mergeCell ref="AP19:AQ19"/>
+    <mergeCell ref="AR19:AS19"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="J25:S25"/>
+    <mergeCell ref="Y25:AH25"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="Y27:AA27"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="J31:S31"/>
     <mergeCell ref="Y31:AH31"/>
@@ -3897,29 +3975,6 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="J30:S30"/>
     <mergeCell ref="Y30:AH30"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="J25:S25"/>
-    <mergeCell ref="Y25:AH25"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="I28:T28"/>
-    <mergeCell ref="X28:AI28"/>
-    <mergeCell ref="AP5:AQ5"/>
-    <mergeCell ref="AR5:AS5"/>
-    <mergeCell ref="A19:AD20"/>
-    <mergeCell ref="AE19:AI19"/>
-    <mergeCell ref="AP19:AQ19"/>
-    <mergeCell ref="AR19:AS19"/>
-    <mergeCell ref="B1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="B2:AP2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E4:S4"/>
-    <mergeCell ref="T4:AI4"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AS4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157499" right="0.23622047244094499" top="0.47244094488188998" bottom="0.23622047244094499" header="0.31496062992126" footer="0.31496062992126"/>
